--- a/jpcore-r4/feature/observateion_endoscopy.valueのバインディングをcodableconceptのみに適用する/StructureDefinition-jp-observation-electrocardiogram-deviceinterpretation.xlsx
+++ b/jpcore-r4/feature/observateion_endoscopy.valueのバインディングをcodableconceptのみに適用する/StructureDefinition-jp-observation-electrocardiogram-deviceinterpretation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>
